--- a/data/trans_bre/P16A07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,91</t>
+          <t>2,03; 10,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,93</t>
+          <t>-0,12; 7,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,93</t>
+          <t>2,11; 9,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,27</t>
+          <t>1,04; 5,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 803,17</t>
+          <t>27,72; 745,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 354,64</t>
+          <t>-7,5; 358,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,23; 667,31</t>
+          <t>39,48; 688,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 913,03</t>
+          <t>15,08; 785,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,34</t>
+          <t>3,01; 7,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,84</t>
+          <t>2,62; 8,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,62</t>
+          <t>2,59; 7,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,78</t>
+          <t>3,21; 9,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>159,07; 2775,03</t>
+          <t>147,18; 2640,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,66; 700,75</t>
+          <t>54,07; 686,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,54; 913,45</t>
+          <t>97,79; 1177,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,38; 333,56</t>
+          <t>52,9; 378,89</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,24</t>
+          <t>0,85; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,23</t>
+          <t>0,98; 8,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,42</t>
+          <t>1,32; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,8</t>
+          <t>0,67; 7,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 1650,42</t>
+          <t>1,8; 1491,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 365,95</t>
+          <t>4,68; 342,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,09; —</t>
+          <t>42,93; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 214,44</t>
+          <t>10,04; 193,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,14</t>
+          <t>1,64; 6,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,16</t>
+          <t>5,79; 12,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,38</t>
+          <t>2,33; 8,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,54</t>
+          <t>-4,25; 2,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,32; 2211,24</t>
+          <t>58,55; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>217,32; 1967,16</t>
+          <t>198,49; 2131,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,74; 933,99</t>
+          <t>67,19; 864,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 84,85</t>
+          <t>-58,41; 91,47</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,35</t>
+          <t>1,99; 12,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 18,09</t>
+          <t>7,85; 18,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 9,01</t>
+          <t>-1,6; 8,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,28</t>
+          <t>1,62; 6,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,59; 479,98</t>
+          <t>19,6; 468,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>123,01; 1349,06</t>
+          <t>133,49; 1362,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 276,17</t>
+          <t>-25,18; 212,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,9; 1458,06</t>
+          <t>43,86; 1612,42</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,82</t>
+          <t>0,37; 5,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 8,67</t>
+          <t>1,12; 9,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,69</t>
+          <t>4,4; 11,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,67</t>
+          <t>-2,02; 4,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; —</t>
+          <t>-26,92; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 406,08</t>
+          <t>14,24; 387,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>176,5; —</t>
+          <t>152,93; 3770,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 132,17</t>
+          <t>-29,95; 127,28</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,05</t>
+          <t>3,42; 8,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,56</t>
+          <t>0,36; 5,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,94</t>
+          <t>1,98; 6,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 5,81</t>
+          <t>-1,67; 5,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>104,43; 641,15</t>
+          <t>105,2; 646,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 180,01</t>
+          <t>4,11; 174,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,79; 748,29</t>
+          <t>67,02; 748,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 150,67</t>
+          <t>-28,49; 149,77</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,17</t>
+          <t>0,8; 5,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,91</t>
+          <t>1,96; 6,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,0</t>
+          <t>2,89; 7,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,6</t>
+          <t>4,64; 8,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,8; 159,94</t>
+          <t>14,21; 173,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,55; 335,87</t>
+          <t>44,35; 339,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,03; 331,77</t>
+          <t>66,99; 333,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>200,68; 1190,35</t>
+          <t>210,33; 1266,81</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,34</t>
+          <t>3,38; 5,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,26</t>
+          <t>4,08; 6,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,94</t>
+          <t>3,92; 6,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,04</t>
+          <t>2,51; 5,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>130,75; 301,93</t>
+          <t>131,42; 291,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>107,3; 230,64</t>
+          <t>109,6; 236,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>155,29; 331,8</t>
+          <t>147,97; 327,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>65,87; 187,79</t>
+          <t>73,01; 191,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>206,91%</t>
+          <t>235,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,22</t>
+          <t>2,55; 10,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,89</t>
+          <t>0,12; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,67</t>
+          <t>2,14; 9,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,3</t>
+          <t>1,3; 5,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 745,01</t>
+          <t>53,5; 822,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 358,72</t>
+          <t>-7,24; 369,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,48; 688,28</t>
+          <t>38,23; 700,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 785,14</t>
+          <t>39,83; 1025,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>163,35%</t>
+          <t>156,22%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,35</t>
+          <t>2,97; 7,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,81</t>
+          <t>2,59; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,62</t>
+          <t>2,64; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,33</t>
+          <t>3,24; 8,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>147,18; 2640,3</t>
+          <t>133,01; 2625,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,07; 686,22</t>
+          <t>39,01; 729,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,79; 1177,7</t>
+          <t>83,74; 1040,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,9; 378,89</t>
+          <t>52,18; 360,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,17</t>
+          <t>0,73; 6,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,67</t>
+          <t>0,74; 9,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,29</t>
+          <t>1,28; 6,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,27</t>
+          <t>0,46; 7,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 1491,16</t>
+          <t>-2,08; 1660,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 342,99</t>
+          <t>2,23; 375,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,93; —</t>
+          <t>20,84; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 193,12</t>
+          <t>2,52; 177,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,96%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,17</t>
+          <t>1,7; 6,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 12,26</t>
+          <t>5,71; 11,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,08</t>
+          <t>2,62; 8,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,59</t>
+          <t>-2,24; 3,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,55; —</t>
+          <t>79,63; 2211,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>198,49; 2131,82</t>
+          <t>212,53; 2061,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,19; 864,77</t>
+          <t>75,47; 873,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 91,47</t>
+          <t>-35,68; 168,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>311,58%</t>
+          <t>332,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 12,25</t>
+          <t>2,33; 13,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 18,48</t>
+          <t>7,07; 17,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,45</t>
+          <t>-0,98; 8,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,39</t>
+          <t>1,5; 6,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,6; 468,28</t>
+          <t>25,83; 499,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133,49; 1362,49</t>
+          <t>115,95; 1307,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 212,76</t>
+          <t>-17,9; 237,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,86; 1612,42</t>
+          <t>39,79; 1591,6</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,14</t>
+          <t>0,51; 5,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,22</t>
+          <t>1,34; 9,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,52</t>
+          <t>4,1; 11,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,23</t>
+          <t>-1,91; 4,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,92; —</t>
+          <t>-22,26; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,24; 387,02</t>
+          <t>19,53; 482,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>152,93; 3770,29</t>
+          <t>142,33; 3757,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 127,28</t>
+          <t>-31,48; 130,08</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,08</t>
+          <t>3,33; 8,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,43</t>
+          <t>0,48; 5,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,19</t>
+          <t>1,83; 5,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,85</t>
+          <t>1,94; 6,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>105,2; 646,34</t>
+          <t>118,41; 668,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 174,29</t>
+          <t>5,7; 195,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,02; 748,03</t>
+          <t>50,42; 790,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 149,77</t>
+          <t>28,79; 196,92</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>461,29%</t>
+          <t>301,24%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,35</t>
+          <t>0,72; 5,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,17</t>
+          <t>1,76; 6,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,84</t>
+          <t>3,18; 8,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,55</t>
+          <t>3,92; 7,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,21; 173,78</t>
+          <t>12,6; 178,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,35; 339,13</t>
+          <t>44,26; 339,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,99; 333,24</t>
+          <t>71,25; 328,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>210,33; 1266,81</t>
+          <t>139,23; 581,51</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>121,83%</t>
+          <t>122,45%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,25</t>
+          <t>3,29; 5,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,39</t>
+          <t>4,01; 6,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,09</t>
+          <t>3,9; 5,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,12</t>
+          <t>3,26; 5,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>131,42; 291,01</t>
+          <t>125,11; 288,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>109,6; 236,2</t>
+          <t>109,06; 236,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>147,97; 327,52</t>
+          <t>151,89; 324,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>73,01; 191,07</t>
+          <t>81,58; 168,06</t>
         </is>
       </c>
     </row>
